--- a/src/test/resources/testdata/EmployeeData.xlsx
+++ b/src/test/resources/testdata/EmployeeData.xlsx
@@ -2,8 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet name="EmployeeData" sheetId="1" r:id="rId1"/>
+    <sheet name="AddEmployee" r:id="rId6" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,12 +34,506 @@
 </metadata>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="163">
+  <si>
+    <t>testCaseId</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>employeeCode</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>designation</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>employmentType</t>
+  </si>
+  <si>
+    <t>joiningDate</t>
+  </si>
+  <si>
+    <t>expectedResult</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_01</t>
+  </si>
+  <si>
+    <t>newuser01@rivio.com</t>
+  </si>
+  <si>
+    <t>Password123!</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>Mitesh</t>
+  </si>
+  <si>
+    <t>Paliwal</t>
+  </si>
+  <si>
+    <t>EMP1001</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Backend Developer</t>
+  </si>
+  <si>
+    <t>Bengaluru HQ</t>
+  </si>
+  <si>
+    <t>FULL_TIME</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Valid full-time engineering onboarding</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_02</t>
+  </si>
+  <si>
+    <t>newuser02@rivio.com</t>
+  </si>
+  <si>
+    <t>Aisha</t>
+  </si>
+  <si>
+    <t>Verma</t>
+  </si>
+  <si>
+    <t>EMP1002</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>HR Executive</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Valid HR onboarding in Mumbai</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_03</t>
+  </si>
+  <si>
+    <t>newuser03@rivio.com</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Iyer</t>
+  </si>
+  <si>
+    <t>EMP1003</t>
+  </si>
+  <si>
+    <t>Engineering Manager</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>Manager-role onboarding</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_04</t>
+  </si>
+  <si>
+    <t>newuser04@rivio.com</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>Nair</t>
+  </si>
+  <si>
+    <t>EMP1004</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>PART_TIME</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>Part-time finance onboarding</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_05</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NoEmail</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>EMP1005</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Empty email — submit must be disabled / form invalid</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_06</t>
+  </si>
+  <si>
+    <t>bad-email-format</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>EMP1006</t>
+  </si>
+  <si>
+    <t>Invalid email format</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_07</t>
+  </si>
+  <si>
+    <t>newuser07@rivio.com</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>EMP1007</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>Weak password (less than 8 chars)</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_08</t>
+  </si>
+  <si>
+    <t>newuser08@rivio.com</t>
+  </si>
+  <si>
+    <t>EMP1008</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>Empty first &amp; last name</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_09</t>
+  </si>
+  <si>
+    <t>newuser09@rivio.com</t>
+  </si>
+  <si>
+    <t>Dup</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>Duplicate employee code (collides with EMP_01)</t>
+  </si>
+  <si>
+    <t>eng.dev.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>EMP{ts}1</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>Flavor 1 — Engineering / Backend / Bengaluru / Full-time</t>
+  </si>
+  <si>
+    <t>hr.exec.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>EMP{ts}2</t>
+  </si>
+  <si>
+    <t>Flavor 2 — HR / Executive / Mumbai / Full-time</t>
+  </si>
+  <si>
+    <t>eng.mgr.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>EMP{ts}3</t>
+  </si>
+  <si>
+    <t>Flavor 3 — Manager role / Engineering</t>
+  </si>
+  <si>
+    <t>fin.pt.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>EMP{ts}4</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>Flavor 4 — Finance / Accountant / Chennai / Part-time</t>
+  </si>
+  <si>
+    <t>sales.con.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>Karan</t>
+  </si>
+  <si>
+    <t>Mehta</t>
+  </si>
+  <si>
+    <t>EMP{ts}5</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Sales Executive</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>Flavor 5 — Sales / Contract / Delhi</t>
+  </si>
+  <si>
+    <t>EMP{ts}6</t>
+  </si>
+  <si>
+    <t>Negative — empty email must block submit</t>
+  </si>
+  <si>
+    <t>EMP{ts}7</t>
+  </si>
+  <si>
+    <t>Negative — malformed email must be rejected</t>
+  </si>
+  <si>
+    <t>noname.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>EMP{ts}8</t>
+  </si>
+  <si>
+    <t>Negative — empty first &amp; last name</t>
+  </si>
+  <si>
+    <t>Negative — empty email (Validators.required)</t>
+  </si>
+  <si>
+    <t>Negative — malformed email (Validators.email)</t>
+  </si>
+  <si>
+    <t>Negative — empty firstName + lastName (both Validators.required)</t>
+  </si>
+  <si>
+    <t>no.pwd.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>NoPwd</t>
+  </si>
+  <si>
+    <t>EMP{ts}9</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>Negative — empty password (Validators.required)</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_10</t>
+  </si>
+  <si>
+    <t>short.pwd.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>Ab12!</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Pwd</t>
+  </si>
+  <si>
+    <t>EMP{ts}A</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>Negative — password 5 chars, minLength(6) violation</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_11</t>
+  </si>
+  <si>
+    <t>no.code.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>NoCode</t>
+  </si>
+  <si>
+    <t>Negative — empty employeeCode (Validators.required)</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_12</t>
+  </si>
+  <si>
+    <t>no.role.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>NoRole</t>
+  </si>
+  <si>
+    <t>EMP{ts}B</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>Negative — no role selected (roleId Validators.required)</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_13</t>
+  </si>
+  <si>
+    <t>no.dept.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>NoDept</t>
+  </si>
+  <si>
+    <t>EMP{ts}C</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>Negative — no department (departmentId + designationId required)</t>
+  </si>
+  <si>
+    <t>RV_ADD_EMP_14</t>
+  </si>
+  <si>
+    <t>no.loc.{ts}@rivio.com</t>
+  </si>
+  <si>
+    <t>NoLoc</t>
+  </si>
+  <si>
+    <t>EMP{ts}D</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>Negative — no location selected (locationId Validators.required)</t>
+  </si>
+  <si>
+    <t>Payroll Specialist</t>
+  </si>
+  <si>
+    <t>Chennai HQ</t>
+  </si>
+  <si>
+    <t>Flavor 4 — Finance / Payroll Specialist / Chennai HQ / Part-time</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -43,13 +541,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,8 +592,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,154 +932,154 @@
   <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="0">
         <v>firstName</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="0">
         <v>lastName</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="0">
         <v>email</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="0">
         <v>phone</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" t="str" s="0">
         <v>dob</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" t="str" s="0">
         <v>gender</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" t="str" s="0">
         <v>department</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" t="str" s="0">
         <v>designation</v>
       </c>
-      <c r="I1" t="str">
+      <c r="I1" t="str" s="0">
         <v>employmentType</v>
       </c>
-      <c r="J1" t="str">
+      <c r="J1" t="str" s="0">
         <v>joinDate</v>
       </c>
-      <c r="K1" t="str">
+      <c r="K1" t="str" s="0">
         <v>location</v>
       </c>
-      <c r="L1" t="str">
+      <c r="L1" t="str" s="0">
         <v>salary</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" t="str" s="0">
         <v>Alice</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" t="str" s="0">
         <v>Smith</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" t="str" s="0">
         <v>alice.smith@rivio.com</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" t="str" s="0">
         <v>9876543210</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E2" t="str" s="0">
         <v>1995-03-15</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F2" t="str" s="0">
         <v>Female</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <v>Engineering</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H2" t="str" s="0">
         <v>Software Engineer</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I2" t="str" s="0">
         <v>FULL_TIME</v>
       </c>
-      <c r="J2" t="str">
+      <c r="J2" t="str" s="0">
         <v>2025-01-01</v>
       </c>
-      <c r="K2" t="str">
+      <c r="K2" t="str" s="0">
         <v>Mumbai</v>
       </c>
-      <c r="L2" t="str">
+      <c r="L2" t="str" s="0">
         <v>80000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" t="str" s="0">
         <v>Bob</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" t="str" s="0">
         <v>Jones</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" t="str" s="0">
         <v>bob.jones@rivio.com</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" t="str" s="0">
         <v>9123456789</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E3" t="str" s="0">
         <v>1990-07-22</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F3" t="str" s="0">
         <v>Male</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" t="str" s="0">
         <v>HR</v>
       </c>
-      <c r="H3" t="str">
+      <c r="H3" t="str" s="0">
         <v>HR Executive</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I3" t="str" s="0">
         <v>FULL_TIME</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J3" t="str" s="0">
         <v>2025-02-01</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K3" t="str" s="0">
         <v>Bangalore</v>
       </c>
-      <c r="L3" t="str">
+      <c r="L3" t="str" s="0">
         <v>60000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" t="str" s="0">
         <v>Carol</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" t="str" s="0">
         <v>Davis</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" t="str" s="0">
         <v>carol.davis@rivio.com</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" t="str" s="0">
         <v>9988776655</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4" t="str" s="0">
         <v>1993-11-05</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F4" t="str" s="0">
         <v>Female</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4" t="str" s="0">
         <v>Finance</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H4" t="str" s="0">
         <v>Accountant</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I4" t="str" s="0">
         <v>FULL_TIME</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J4" t="str" s="0">
         <v>2025-03-01</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K4" t="str" s="0">
         <v>Chennai</v>
       </c>
-      <c r="L4" t="str">
+      <c r="L4" t="str" s="0">
         <v>55000</v>
       </c>
     </row>
@@ -556,4 +1088,690 @@
     <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="15.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="21.51953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.2578125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="8.34375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="8.01953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="12.125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="10.421875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="18.078125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="12.11328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.10546875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="10.140625" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="12.44921875" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="55.734375" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="4">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="4">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="4">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="4">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="4">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="4">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s" s="4">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s" s="4">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s" s="4">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s" s="4">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s" s="4">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s" s="4">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K12" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L12" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I13" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K13" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="I14" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="K14" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L14" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="M14" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="K15" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L15" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>